--- a/Startups Growth Part2.xlsx
+++ b/Startups Growth Part2.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B545467-BC7D-42E2-884C-E52315E619B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BFD480-86CB-4F36-8C07-4BB2D76240C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{5F0A02C3-7BF7-4D2A-BE80-9445058783F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{5F0A02C3-7BF7-4D2A-BE80-9445058783F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Incubators_Presence" sheetId="2" r:id="rId1"/>
     <sheet name="Incubators_Support_Startups" sheetId="3" r:id="rId2"/>
     <sheet name="Funding_to_Startups" sheetId="5" r:id="rId3"/>
-    <sheet name="Funding" sheetId="7" r:id="rId4"/>
+    <sheet name="Ministry_Funding" sheetId="7" r:id="rId4"/>
     <sheet name="Ministries_support_Techstartups" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="121">
   <si>
     <t>State/UT</t>
   </si>
@@ -180,12 +180,6 @@
     <t>Amount Approved to Startups (in Rs. Crore) - 2023</t>
   </si>
   <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
     <t>3.803</t>
   </si>
   <si>
@@ -216,18 +210,12 @@
     <t>0.94</t>
   </si>
   <si>
-    <t>2.24</t>
-  </si>
-  <si>
     <t>5.215</t>
   </si>
   <si>
     <t>14.55</t>
   </si>
   <si>
-    <t>0.9</t>
-  </si>
-  <si>
     <t>0.55</t>
   </si>
   <si>
@@ -264,9 +252,6 @@
     <t>0.5</t>
   </si>
   <si>
-    <t>4.07</t>
-  </si>
-  <si>
     <t>22.07</t>
   </si>
   <si>
@@ -279,18 +264,12 @@
     <t>3.47</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
     <t>5.45</t>
   </si>
   <si>
     <t>4.8403</t>
   </si>
   <si>
-    <t>2.2</t>
-  </si>
-  <si>
     <t>16.33</t>
   </si>
   <si>
@@ -327,27 +306,18 @@
     <t>6.35</t>
   </si>
   <si>
-    <t>3.025</t>
-  </si>
-  <si>
     <t>7.791</t>
   </si>
   <si>
     <t>14.524</t>
   </si>
   <si>
-    <t>0.65</t>
-  </si>
-  <si>
     <t>9.015</t>
   </si>
   <si>
     <t>12.505</t>
   </si>
   <si>
-    <t>2.005</t>
-  </si>
-  <si>
     <t>5.893</t>
   </si>
   <si>
@@ -357,9 +327,6 @@
     <t>1.4</t>
   </si>
   <si>
-    <t>0.565</t>
-  </si>
-  <si>
     <t>1.26</t>
   </si>
   <si>
@@ -451,6 +418,9 @@
   </si>
   <si>
     <t>Sum of Funding Disbursed (Rs. in Crore)</t>
+  </si>
+  <si>
+    <t>Amount Approved to Startups (in Rs. Crore) - 2024</t>
   </si>
 </sst>
 </file>
@@ -472,15 +442,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -488,11 +464,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -509,11 +496,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="31">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -525,6 +542,34 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -550,21 +595,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -854,12 +884,13 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="3" xr16:uid="{45B15FC9-0086-48C9-8CC4-7A3989F938EE}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
-    <queryTableFields count="4">
+  <queryTableRefresh nextId="9" unboundColumnsRight="1">
+    <queryTableFields count="5">
       <queryTableField id="2" name="Column2" tableColumnId="2"/>
       <queryTableField id="3" name="Column3" tableColumnId="3"/>
       <queryTableField id="4" name="Column4" tableColumnId="4"/>
       <queryTableField id="5" name="Column5" tableColumnId="5"/>
+      <queryTableField id="8" dataBound="0" tableColumnId="1"/>
     </queryTableFields>
     <queryTableDeletedFields count="1">
       <deletedField name="Column1"/>
@@ -891,8 +922,8 @@
     <sortCondition descending="1" ref="B1:B28"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{4ED6A15A-6253-4183-AE7F-A224FAE0B958}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{0FDE9869-4116-409C-AB83-C525C75D2F20}" uniqueName="3" name="Number of Incubators" totalsRowFunction="custom" queryTableFieldId="3" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="2" xr3:uid="{4ED6A15A-6253-4183-AE7F-A224FAE0B958}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{0FDE9869-4116-409C-AB83-C525C75D2F20}" uniqueName="3" name="Number of Incubators" totalsRowFunction="custom" queryTableFieldId="3" dataDxfId="28" totalsRowDxfId="27">
       <totalsRowFormula>SUM(incubators_startup[Number of Incubators])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -907,11 +938,11 @@
     <sortCondition descending="1" ref="E1:E33"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{89DBE995-2A98-4089-979B-481EB0784E04}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{82663536-EB40-4922-9BC9-3EB5FB5B0EDA}" uniqueName="3" name="Number of Startups - 2021" queryTableFieldId="3" dataDxfId="19" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{2DE6F75E-BC8D-48B8-8A1D-7D495EAEB13F}" uniqueName="4" name="Number of Startups - 2022" queryTableFieldId="4" dataDxfId="18" totalsRowDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{8176493F-C5CA-44BD-9B00-64097CBEF5CC}" uniqueName="5" name="Number of Startups - 2023" queryTableFieldId="5" dataDxfId="17" totalsRowDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{EDFBC78E-A097-4AC0-9C82-A47024D85C57}" uniqueName="1" name="Sum of Starups Supported" totalsRowFunction="custom" queryTableFieldId="6" dataDxfId="16" totalsRowDxfId="4">
+    <tableColumn id="2" xr3:uid="{89DBE995-2A98-4089-979B-481EB0784E04}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{82663536-EB40-4922-9BC9-3EB5FB5B0EDA}" uniqueName="3" name="Number of Startups - 2021" queryTableFieldId="3" dataDxfId="25" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{2DE6F75E-BC8D-48B8-8A1D-7D495EAEB13F}" uniqueName="4" name="Number of Startups - 2022" queryTableFieldId="4" dataDxfId="24" totalsRowDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{8176493F-C5CA-44BD-9B00-64097CBEF5CC}" uniqueName="5" name="Number of Startups - 2023" queryTableFieldId="5" dataDxfId="23" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{EDFBC78E-A097-4AC0-9C82-A47024D85C57}" uniqueName="1" name="Sum of Starups Supported" totalsRowFunction="custom" queryTableFieldId="6" dataDxfId="22" totalsRowDxfId="14">
       <calculatedColumnFormula>SUM(B2:D2)</calculatedColumnFormula>
       <totalsRowFormula>SUM(incubationsupport[Sum of Starups Supported])</totalsRowFormula>
     </tableColumn>
@@ -921,26 +952,39 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AFC21407-0216-4205-8BF1-99D8269BBD42}" name="startup_fuinding" displayName="startup_fuinding" ref="A1:D34" tableType="queryTable" totalsRowCount="1">
-  <autoFilter ref="A1:D33" xr:uid="{AFC21407-0216-4205-8BF1-99D8269BBD42}"/>
-  <tableColumns count="4">
-    <tableColumn id="2" xr3:uid="{4F8D4A3F-88D6-4E52-8ABF-EF5908C8D78A}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="15" totalsRowDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{C20ED446-C988-40F4-A5CE-CF08A467C958}" uniqueName="3" name="Amount Approved to Startups (in Rs. Crore) - 2021" queryTableFieldId="3" dataDxfId="14" totalsRowDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{55779E72-5FAE-4B73-8BEE-0C3397DD6253}" uniqueName="4" name="Amount Approved to Startups (in Rs. Crore) - 2022" queryTableFieldId="4" dataDxfId="13" totalsRowDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{197243C9-AC92-40AF-BCE6-BCD6F1AC5F16}" uniqueName="5" name="Amount Approved to Startups (in Rs. Crore) - 2023" queryTableFieldId="5" dataDxfId="12" totalsRowDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AFC21407-0216-4205-8BF1-99D8269BBD42}" name="startup_fuinding" displayName="startup_fuinding" ref="A1:E34" tableType="queryTable" totalsRowCount="1">
+  <autoFilter ref="A1:E33" xr:uid="{AFC21407-0216-4205-8BF1-99D8269BBD42}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E33">
+    <sortCondition descending="1" ref="E1:E33"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="2" xr3:uid="{4F8D4A3F-88D6-4E52-8ABF-EF5908C8D78A}" uniqueName="2" name="State/UT" queryTableFieldId="2" dataDxfId="9" totalsRowDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{C20ED446-C988-40F4-A5CE-CF08A467C958}" uniqueName="3" name="Amount Approved to Startups (in Rs. Crore) - 2021" totalsRowFunction="custom" queryTableFieldId="3" dataDxfId="8" totalsRowDxfId="4">
+      <totalsRowFormula>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2021]])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{55779E72-5FAE-4B73-8BEE-0C3397DD6253}" uniqueName="4" name="Amount Approved to Startups (in Rs. Crore) - 2022" totalsRowFunction="custom" queryTableFieldId="4" dataDxfId="7" totalsRowDxfId="3">
+      <totalsRowFormula>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2022]])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{197243C9-AC92-40AF-BCE6-BCD6F1AC5F16}" uniqueName="5" name="Amount Approved to Startups (in Rs. Crore) - 2023" totalsRowFunction="custom" queryTableFieldId="5" dataDxfId="6" totalsRowDxfId="2">
+      <totalsRowFormula>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2023]])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{75C042E4-B0E1-4942-8A1B-2484C470F5E0}" uniqueName="1" name="Amount Approved to Startups (in Rs. Crore) - 2024" totalsRowFunction="custom" queryTableFieldId="8" dataDxfId="0" totalsRowDxfId="1">
+      <calculatedColumnFormula>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</calculatedColumnFormula>
+      <totalsRowFormula>SUM(startup_fuinding[[#Totals],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{42FFE187-4270-4DF9-9FE5-366BBA0F7DB7}" name="Techstartups_help" displayName="Techstartups_help" ref="A1:D12" tableType="queryTable" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{42FFE187-4270-4DF9-9FE5-366BBA0F7DB7}" name="Techstartups_help" displayName="Techstartups_help" ref="A1:D13" tableType="queryTable" totalsRowCount="1">
   <autoFilter ref="A1:D12" xr:uid="{42FFE187-4270-4DF9-9FE5-366BBA0F7DB7}"/>
   <tableColumns count="4">
-    <tableColumn id="2" xr3:uid="{2734F1EC-245C-4C6A-989D-51102DF55F74}" uniqueName="2" name="Ministry/ Department" queryTableFieldId="2" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{770D73D5-D1B6-4714-8AC9-1F1093185F05}" uniqueName="3" name="Scheme/ Programme" queryTableFieldId="3" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{3B336725-B867-474B-8C26-6C37AEFC69AE}" uniqueName="4" name="No. of Tech Startups Supported" queryTableFieldId="4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{9C3E2301-4462-426F-A455-97713F8503BC}" uniqueName="5" name="Funding Disbursed (Rs. in Crore)" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{2734F1EC-245C-4C6A-989D-51102DF55F74}" uniqueName="2" name="Ministry/ Department" queryTableFieldId="2" dataDxfId="21" totalsRowDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{770D73D5-D1B6-4714-8AC9-1F1093185F05}" uniqueName="3" name="Scheme/ Programme" queryTableFieldId="3" dataDxfId="20" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{3B336725-B867-474B-8C26-6C37AEFC69AE}" uniqueName="4" name="No. of Tech Startups Supported" queryTableFieldId="4" dataDxfId="19" totalsRowDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{9C3E2301-4462-426F-A455-97713F8503BC}" uniqueName="5" name="Funding Disbursed (Rs. in Crore)" queryTableFieldId="5" dataDxfId="18" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1512,7 +1556,7 @@
         <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -2111,14 +2155,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C414DB-6F39-435D-87E5-116B91E86A70}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="43.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2131,460 +2175,604 @@
       <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="12">
+        <v>4.07</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="14">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>3.0249999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>2.0049999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="10">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.56499999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B20" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="E20">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="13">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="E22">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E23">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E24">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>127</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E33">
+        <f>SUM(startup_fuinding[[#This Row],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="B34" s="7">
+        <f>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2021]])</f>
+        <v>20.854999999999997</v>
+      </c>
+      <c r="C34" s="7">
+        <f>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2022]])</f>
+        <v>0.78</v>
+      </c>
+      <c r="D34" s="7">
+        <f>SUM(startup_fuinding[[#Headers],[#Data],[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="E34" s="1">
+        <f>SUM(startup_fuinding[[#Totals],[Amount Approved to Startups (in Rs. Crore) - 2021]:[Amount Approved to Startups (in Rs. Crore) - 2023]])</f>
+        <v>21.674999999999997</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2597,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2581E8DA-8812-4B81-93EF-F3029D733071}">
-  <dimension ref="A3:C7"/>
+  <dimension ref="A3:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.6328125" bestFit="1" customWidth="1"/>
@@ -2617,18 +2805,18 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B4">
         <v>1777</v>
@@ -2639,7 +2827,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B5">
         <v>490</v>
@@ -2650,7 +2838,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B6">
         <v>3638</v>
@@ -2661,13 +2849,19 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B7">
         <v>4106</v>
       </c>
       <c r="C7" s="5">
         <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v>580.20000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -2677,7 +2871,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A20325-7D97-4368-B7C3-73F16FAC01F5}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.6328125" bestFit="1" customWidth="1"/>
@@ -2688,24 +2882,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C2" s="1">
         <v>1235</v>
@@ -2716,10 +2910,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C3" s="1">
         <v>175</v>
@@ -2730,10 +2924,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1">
         <v>530</v>
@@ -2744,10 +2938,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1">
         <v>398</v>
@@ -2758,10 +2952,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1">
         <v>1205</v>
@@ -2772,10 +2966,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
@@ -2786,10 +2980,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -2800,10 +2994,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1">
         <v>35</v>
@@ -2814,10 +3008,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1">
         <v>4106</v>
@@ -2828,10 +3022,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C11" s="1">
         <v>490</v>
@@ -2842,10 +3036,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C12" s="1">
         <v>1777</v>
@@ -2853,6 +3047,12 @@
       <c r="D12" s="2">
         <v>195.8</v>
       </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
